--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kang/Documents/GitHub/dear-data-100/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B9EB22A-EC1A-264F-A56F-9AF74F6709A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14EEDD60-2394-E849-97C0-480785A5BF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2100" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{091FBDB8-D6A6-164D-83CE-25988338598D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
@@ -639,10 +639,25 @@
       <c r="B14" t="s">
         <v>2</v>
       </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kang/Documents/GitHub/dear-data-100/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14EEDD60-2394-E849-97C0-480785A5BF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2116E477-8A9F-E047-9B85-D7E91F5DC1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2100" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{091FBDB8-D6A6-164D-83CE-25988338598D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
@@ -667,13 +667,25 @@
       <c r="B16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>46323</v>
       </c>
@@ -681,12 +693,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>46324</v>
       </c>
@@ -694,12 +706,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>46325</v>
       </c>
@@ -707,12 +719,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>46326</v>
       </c>
@@ -720,12 +732,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>46327</v>
       </c>
@@ -733,12 +745,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>46328</v>
       </c>
@@ -746,12 +758,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>46329</v>
       </c>
@@ -759,7 +771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>3</v>
       </c>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kang/Documents/GitHub/dear-data-100/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2116E477-8A9F-E047-9B85-D7E91F5DC1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35A8602-30CA-4A40-AF0F-652878EC2B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2100" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{091FBDB8-D6A6-164D-83CE-25988338598D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
@@ -692,10 +692,28 @@
       <c r="B18" t="s">
         <v>2</v>
       </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kang/Documents/GitHub/dear-data-100/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35A8602-30CA-4A40-AF0F-652878EC2B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FD5FBD-F437-1244-9DA1-ADE44F4C80D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2100" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{091FBDB8-D6A6-164D-83CE-25988338598D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
@@ -723,10 +723,25 @@
       <c r="B20" t="s">
         <v>2</v>
       </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kang/Documents/GitHub/dear-data-100/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FD5FBD-F437-1244-9DA1-ADE44F4C80D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13441CB-D262-1A45-91A2-918C3E2189BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2100" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{091FBDB8-D6A6-164D-83CE-25988338598D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
@@ -751,10 +751,25 @@
       <c r="B22" t="s">
         <v>2</v>
       </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kang/Documents/GitHub/dear-data-100/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13441CB-D262-1A45-91A2-918C3E2189BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0531FB94-2FD5-584D-BB64-C8CC5DEA0FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2100" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{091FBDB8-D6A6-164D-83CE-25988338598D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
@@ -779,10 +779,25 @@
       <c r="B24" t="s">
         <v>2</v>
       </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
